--- a/assessment_forms/044_facility_features_assessment--assessment_forms.xlsx
+++ b/assessment_forms/044_facility_features_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'residential',_'value':_'residential'}</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Residential', 'value': 'Residential'}</t>
+          <t>Residential</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'commercial',_'value':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Commercial', 'value': 'Commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'industrial',_'value':_'industrial'}</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Industrial', 'value': 'Industrial'}</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'parking_lot',_'value':_'parking_lot'}</t>
+          <t>parking_lot</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Parking Lot', 'value': 'Parking Lot'}</t>
+          <t>Parking Lot</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'restroom',_'value':_'restroom'}</t>
+          <t>restroom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Restroom', 'value': 'Restroom'}</t>
+          <t>Restroom</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'elevator',_'value':_'elevator'}</t>
+          <t>elevator</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Elevator', 'value': 'Elevator'}</t>
+          <t>Elevator</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'security_system',_'value':_'security_system'}</t>
+          <t>security_system</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Security System', 'value': 'Security System'}</t>
+          <t>Security System</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'brick',_'value':_'brick'}</t>
+          <t>brick</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Brick', 'value': 'Brick'}</t>
+          <t>Brick</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'concrete',_'value':_'concrete'}</t>
+          <t>concrete</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Concrete', 'value': 'Concrete'}</t>
+          <t>Concrete</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'steel',_'value':_'steel'}</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Steel', 'value': 'Steel'}</t>
+          <t>Steel</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'glass',_'value':_'glass'}</t>
+          <t>glass</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Glass', 'value': 'Glass'}</t>
+          <t>Glass</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'circuit_breaker',_'value':_'circuit_breaker'}</t>
+          <t>circuit_breaker</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Circuit Breaker', 'value': 'Circuit Breaker'}</t>
+          <t>Circuit Breaker</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'generator',_'value':_'generator'}</t>
+          <t>generator</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Generator', 'value': 'Generator'}</t>
+          <t>Generator</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'solar_panel',_'value':_'solar_panel'}</t>
+          <t>solar_panel</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Solar Panel', 'value': 'Solar Panel'}</t>
+          <t>Solar Panel</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'water_heater',_'value':_'water_heater'}</t>
+          <t>water_heater</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Water Heater', 'value': 'Water Heater'}</t>
+          <t>Water Heater</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'fire_hydrant',_'value':_'fire_hydrant'}</t>
+          <t>fire_hydrant</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Fire Hydrant', 'value': 'Fire Hydrant'}</t>
+          <t>Fire Hydrant</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'sump_pump',_'value':_'sump_pump'}</t>
+          <t>sump_pump</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Sump Pump', 'value': 'Sump Pump'}</t>
+          <t>Sump Pump</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'central_a/c',_'value':_'central_a/c'}</t>
+          <t>central_a/c</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Central A/C', 'value': 'Central A/C'}</t>
+          <t>Central A/C</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'radiant_heat',_'value':_'radiant_heat'}</t>
+          <t>radiant_heat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Radiant Heat', 'value': 'Radiant Heat'}</t>
+          <t>Radiant Heat</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'heat_pump',_'value':_'heat_pump'}</t>
+          <t>heat_pump</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Heat Pump', 'value': 'Heat Pump'}</t>
+          <t>Heat Pump</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'fire_alarm',_'value':_'fire_alarm'}</t>
+          <t>fire_alarm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Fire Alarm', 'value': 'Fire Alarm'}</t>
+          <t>Fire Alarm</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'fire_suppression',_'value':_'fire_suppression'}</t>
+          <t>fire_suppression</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Fire Suppression', 'value': 'Fire Suppression'}</t>
+          <t>Fire Suppression</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'security_camera',_'value':_'security_camera'}</t>
+          <t>security_camera</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Security Camera', 'value': 'Security Camera'}</t>
+          <t>Security Camera</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'fire_drill',_'value':_'fire_drill'}</t>
+          <t>fire_drill</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Fire Drill', 'value': 'Fire Drill'}</t>
+          <t>Fire Drill</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'emergency_exit',_'value':_'emergency_exit'}</t>
+          <t>emergency_exit</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Emergency Exit', 'value': 'Emergency Exit'}</t>
+          <t>Emergency Exit</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'evacuation_route',_'value':_'evacuation_route'}</t>
+          <t>evacuation_route</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Evacuation Route', 'value': 'Evacuation Route'}</t>
+          <t>Evacuation Route</t>
         </is>
       </c>
     </row>
